--- a/empresas/ejemplo-alimentos-del-sur/datos/alcance3.xlsx
+++ b/empresas/ejemplo-alimentos-del-sur/datos/alcance3.xlsx
@@ -893,7 +893,7 @@
       <c r="J15" s="0"/>
       <c r="K15" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Compra de fruta a terceros</t>
+          <t xml:space="preserve">Compra de fruta a terceros. Aproximacion declarada: el catalogo no tiene factor de fruta y se usa el de granos sin procesar.</t>
         </is>
       </c>
     </row>
